--- a/data/inventory_requests.xlsx
+++ b/data/inventory_requests.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="47">
   <si>
     <t>RequestID</t>
   </si>
@@ -68,6 +68,9 @@
   </si>
   <si>
     <t>2025-06-23 22:55</t>
+  </si>
+  <si>
+    <t>2025-07-15 20:01</t>
   </si>
   <si>
     <t>UREA</t>
@@ -122,6 +125,9 @@
     <t>DG39001</t>
   </si>
   <si>
+    <t>DG23000</t>
+  </si>
+  <si>
     <t>admin</t>
   </si>
   <si>
@@ -147,6 +153,9 @@
   </si>
   <si>
     <t>SR94312</t>
+  </si>
+  <si>
+    <t>SR05407</t>
   </si>
 </sst>
 </file>
@@ -504,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -541,19 +550,19 @@
         <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2">
         <v>200</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -561,19 +570,19 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3">
         <v>50</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -581,19 +590,19 @@
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -601,22 +610,22 @@
         <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5">
         <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -624,22 +633,22 @@
         <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E6">
         <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -647,22 +656,22 @@
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -670,22 +679,22 @@
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8">
         <v>20</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -693,22 +702,22 @@
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9">
         <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -716,22 +725,22 @@
         <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10">
         <v>20</v>
       </c>
       <c r="F10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -739,22 +748,45 @@
         <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E11">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12">
+        <v>194</v>
+      </c>
+      <c r="F12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" t="s">
         <v>36</v>
       </c>
-      <c r="I11" t="s">
-        <v>43</v>
+      <c r="H12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/data/inventory_requests.xlsx
+++ b/data/inventory_requests.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="50">
   <si>
     <t>RequestID</t>
   </si>
@@ -71,6 +71,9 @@
   </si>
   <si>
     <t>2025-07-15 20:01</t>
+  </si>
+  <si>
+    <t>2025-08-14 18:43</t>
   </si>
   <si>
     <t>UREA</t>
@@ -128,6 +131,9 @@
     <t>DG23000</t>
   </si>
   <si>
+    <t>Food crops by Growers</t>
+  </si>
+  <si>
     <t>admin</t>
   </si>
   <si>
@@ -156,6 +162,9 @@
   </si>
   <si>
     <t>SR05407</t>
+  </si>
+  <si>
+    <t>SR06968</t>
   </si>
 </sst>
 </file>
@@ -513,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -550,19 +559,19 @@
         <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2">
         <v>200</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -570,19 +579,19 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3">
         <v>50</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -590,19 +599,19 @@
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -610,22 +619,22 @@
         <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5">
         <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -633,22 +642,22 @@
         <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6">
         <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -656,22 +665,22 @@
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -679,22 +688,22 @@
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8">
         <v>20</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -702,22 +711,22 @@
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9">
         <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -725,22 +734,22 @@
         <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E10">
         <v>20</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -748,22 +757,22 @@
         <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E11">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -771,22 +780,45 @@
         <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E12">
         <v>194</v>
       </c>
       <c r="F12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I12" t="s">
-        <v>46</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13">
+        <v>15</v>
+      </c>
+      <c r="F13" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/data/inventory_requests.xlsx
+++ b/data/inventory_requests.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,6 +631,211 @@
         <v>46091.96784585648</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SR1773303862</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>46093.35025532408</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SURF 1kg pocket</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Field Office</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>cjanuary</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Issued</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>psibale</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>46093.39473967592</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SR1773303862</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>46093.35025532408</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TOILET TISSUE DOBLE PLY</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Field Office</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>cjanuary</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Issued</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>psibale</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>46093.39478344908</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SR1773303862</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>46093.35025532408</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Office Tray</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AM Ofice</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>cjanuary</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Issued</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>psibale</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>46093.39481524305</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SR1773303862</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>46093.35025532408</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SOFT BROOMS</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Field Ofice</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>cjanuary</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Issued</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>psibale</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>46093.39484579861</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SR1773303862</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>46093.35025532408</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>A4 HARDCOVER BOOK</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Field Foreman 2</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>cjanuary</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Issued</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>psibale</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>46093.39488327546</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
